--- a/ConfigExporter/xlsx/duel_ai_difficulty.xlsx
+++ b/ConfigExporter/xlsx/duel_ai_difficulty.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -528,6 +528,51 @@
           <t>AI思考延迟毫秒</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>9路实时访问上限</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>13路实时访问上限</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>19路实时访问上限</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>9路候选点数量</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>13路候选点数量</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>19路候选点数量</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>9路最大亏损目数</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>13路最大亏损目数</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>19路最大亏损目数</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -605,6 +650,51 @@
           <t>thinkDelayMs</t>
         </is>
       </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>realtimeMaxVisits9</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>realtimeMaxVisits13</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>realtimeMaxVisits19</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>candidateLimit9</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>candidateLimit13</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>candidateLimit19</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>maxScoreLoss9</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>maxScoreLoss13</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>maxScoreLoss19</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -682,6 +772,51 @@
           <t>int</t>
         </is>
       </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -759,6 +894,51 @@
           <t>#require</t>
         </is>
       </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -822,6 +1002,33 @@
       <c r="O5" t="n">
         <v>450</v>
       </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="n">
+        <v>20</v>
+      </c>
+      <c r="U5" t="n">
+        <v>20</v>
+      </c>
+      <c r="V5" t="n">
+        <v>30</v>
+      </c>
+      <c r="W5" t="n">
+        <v>30</v>
+      </c>
+      <c r="X5" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -885,6 +1092,33 @@
       <c r="O6" t="n">
         <v>500</v>
       </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>18</v>
+      </c>
+      <c r="T6" t="n">
+        <v>18</v>
+      </c>
+      <c r="U6" t="n">
+        <v>18</v>
+      </c>
+      <c r="V6" t="n">
+        <v>24</v>
+      </c>
+      <c r="W6" t="n">
+        <v>24</v>
+      </c>
+      <c r="X6" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -923,7 +1157,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
         <v>16</v>
@@ -947,6 +1181,33 @@
       </c>
       <c r="O7" t="n">
         <v>550</v>
+      </c>
+      <c r="P7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>16</v>
+      </c>
+      <c r="T7" t="n">
+        <v>16</v>
+      </c>
+      <c r="U7" t="n">
+        <v>16</v>
+      </c>
+      <c r="V7" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" t="n">
+        <v>18</v>
+      </c>
+      <c r="X7" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -986,7 +1247,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
         <v>14</v>
@@ -1010,6 +1271,33 @@
       </c>
       <c r="O8" t="n">
         <v>600</v>
+      </c>
+      <c r="P8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>6</v>
+      </c>
+      <c r="R8" t="n">
+        <v>4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>14</v>
+      </c>
+      <c r="T8" t="n">
+        <v>14</v>
+      </c>
+      <c r="U8" t="n">
+        <v>14</v>
+      </c>
+      <c r="V8" t="n">
+        <v>12</v>
+      </c>
+      <c r="W8" t="n">
+        <v>12</v>
+      </c>
+      <c r="X8" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -1049,7 +1337,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="I9" t="n">
         <v>10</v>
@@ -1073,6 +1361,33 @@
       </c>
       <c r="O9" t="n">
         <v>700</v>
+      </c>
+      <c r="P9" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>48</v>
+      </c>
+      <c r="R9" t="n">
+        <v>32</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="n">
+        <v>10</v>
+      </c>
+      <c r="U9" t="n">
+        <v>10</v>
+      </c>
+      <c r="V9" t="n">
+        <v>7</v>
+      </c>
+      <c r="W9" t="n">
+        <v>7</v>
+      </c>
+      <c r="X9" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -1112,7 +1427,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>96</v>
+        <v>160</v>
       </c>
       <c r="I10" t="n">
         <v>7</v>
@@ -1136,6 +1451,33 @@
       </c>
       <c r="O10" t="n">
         <v>850</v>
+      </c>
+      <c r="P10" t="n">
+        <v>160</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>128</v>
+      </c>
+      <c r="R10" t="n">
+        <v>96</v>
+      </c>
+      <c r="S10" t="n">
+        <v>7</v>
+      </c>
+      <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>7</v>
+      </c>
+      <c r="V10" t="n">
+        <v>3</v>
+      </c>
+      <c r="W10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="11">
@@ -1200,6 +1542,33 @@
       <c r="O11" t="n">
         <v>1050</v>
       </c>
+      <c r="P11" t="n">
+        <v>320</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>224</v>
+      </c>
+      <c r="R11" t="n">
+        <v>160</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>5</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1263,6 +1632,33 @@
       <c r="O12" t="n">
         <v>1200</v>
       </c>
+      <c r="P12" t="n">
+        <v>512</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>320</v>
+      </c>
+      <c r="R12" t="n">
+        <v>224</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1326,6 +1722,33 @@
       <c r="O13" t="n">
         <v>1300</v>
       </c>
+      <c r="P13" t="n">
+        <v>640</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>384</v>
+      </c>
+      <c r="R13" t="n">
+        <v>256</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1389,6 +1812,33 @@
       <c r="O14" t="n">
         <v>1400</v>
       </c>
+      <c r="P14" t="n">
+        <v>720</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>448</v>
+      </c>
+      <c r="R14" t="n">
+        <v>288</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1452,6 +1902,33 @@
       <c r="O15" t="n">
         <v>1500</v>
       </c>
+      <c r="P15" t="n">
+        <v>800</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>512</v>
+      </c>
+      <c r="R15" t="n">
+        <v>320</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1515,6 +1992,33 @@
       <c r="O16" t="n">
         <v>1550</v>
       </c>
+      <c r="P16" t="n">
+        <v>800</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>512</v>
+      </c>
+      <c r="R16" t="n">
+        <v>320</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1577,6 +2081,33 @@
       </c>
       <c r="O17" t="n">
         <v>1600</v>
+      </c>
+      <c r="P17" t="n">
+        <v>800</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>512</v>
+      </c>
+      <c r="R17" t="n">
+        <v>320</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>

--- a/ConfigExporter/xlsx/duel_ai_difficulty.xlsx
+++ b/ConfigExporter/xlsx/duel_ai_difficulty.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X17"/>
+  <dimension ref="A1:AU17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -573,6 +573,121 @@
           <t>19路最大亏损目数</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>动态预算开关</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>9路探测访问次数</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>13路探测访问次数</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>19路探测访问次数</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>9路开局探测手数</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>13路开局探测手数</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>19路开局探测手数</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>9路接近局势目差阈值</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>13路接近局势目差阈值</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>19路接近局势目差阈值</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>9路接近胜率阈值</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>13路接近胜率阈值</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>19路接近胜率阈值</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>9路简单候选差距阈值</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>13路简单候选差距阈值</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>19路简单候选差距阈值</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>9路明显首选差距阈值</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>13路明显首选差距阈值</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>19路明显首选差距阈值</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>9路强制完整预算手数</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>13路强制完整预算手数</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>19路强制完整预算手数</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>探测最小候选数量</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -695,6 +810,121 @@
           <t>maxScoreLoss19</t>
         </is>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>dynamicBudgetEnabled</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>probeMaxVisits9</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>probeMaxVisits13</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>probeMaxVisits19</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>openingProbeMoveLimit9</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>openingProbeMoveLimit13</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>openingProbeMoveLimit19</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>closeScoreLeadThreshold9</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>closeScoreLeadThreshold13</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>closeScoreLeadThreshold19</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>closeWinrateThreshold9</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>closeWinrateThreshold13</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>closeWinrateThreshold19</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>simpleCandidateGapThreshold9</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>simpleCandidateGapThreshold13</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>simpleCandidateGapThreshold19</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>confidentBestMoveGapThreshold9</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>confidentBestMoveGapThreshold13</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>confidentBestMoveGapThreshold19</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>forceFullBudgetMoveLimit9</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>forceFullBudgetMoveLimit13</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>forceFullBudgetMoveLimit19</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>probeMinMoveInfoCount</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -817,6 +1047,121 @@
           <t>float</t>
         </is>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -939,6 +1284,121 @@
           <t>#require</t>
         </is>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1029,6 +1489,77 @@
       <c r="X5" t="n">
         <v>30</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1119,6 +1650,77 @@
       <c r="X6" t="n">
         <v>24</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1209,6 +1811,77 @@
       <c r="X7" t="n">
         <v>18</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1299,6 +1972,77 @@
       <c r="X8" t="n">
         <v>12</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1389,6 +2133,77 @@
       <c r="X9" t="n">
         <v>7</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1479,6 +2294,77 @@
       <c r="X10" t="n">
         <v>3.2</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1569,6 +2455,77 @@
       <c r="X11" t="n">
         <v>1.4</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z11" t="n">
+        <v>96</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>90</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>150</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1659,6 +2616,77 @@
       <c r="X12" t="n">
         <v>0.9</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z12" t="n">
+        <v>96</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>90</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>150</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1749,6 +2777,77 @@
       <c r="X13" t="n">
         <v>0.6</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>90</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>150</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1839,6 +2938,77 @@
       <c r="X14" t="n">
         <v>0.4</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z14" t="n">
+        <v>128</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>48</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>90</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>150</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1929,6 +3099,77 @@
       <c r="X15" t="n">
         <v>0.3</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z15" t="n">
+        <v>96</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>90</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>150</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2019,6 +3260,77 @@
       <c r="X16" t="n">
         <v>0.2</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z16" t="n">
+        <v>96</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>90</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>150</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2108,6 +3420,77 @@
       </c>
       <c r="X17" t="n">
         <v>0.1</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z17" t="n">
+        <v>96</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>90</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>150</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/ConfigExporter/xlsx/duel_ai_difficulty.xlsx
+++ b/ConfigExporter/xlsx/duel_ai_difficulty.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU17"/>
+  <dimension ref="A1:AV16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -485,205 +485,210 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>HumanPolicy使用概率</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>包含Policy输出</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>最大访问次数</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>候选点数量</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>失误概率</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>采样温度</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>最大亏损目数</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>访问权重指数</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>终局前允许Pass</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>AI思考延迟毫秒</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>9路实时访问上限</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>13路实时访问上限</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>19路实时访问上限</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>9路候选点数量</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>13路候选点数量</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>19路候选点数量</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>9路最大亏损目数</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>13路最大亏损目数</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>19路最大亏损目数</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>动态预算开关</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>9路探测访问次数</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>13路探测访问次数</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>19路探测访问次数</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>9路开局探测手数</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>13路开局探测手数</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>19路开局探测手数</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>9路接近局势目差阈值</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>13路接近局势目差阈值</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>19路接近局势目差阈值</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>9路接近胜率阈值</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>13路接近胜率阈值</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>19路接近胜率阈值</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>9路简单候选差距阈值</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>13路简单候选差距阈值</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>19路简单候选差距阈值</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>9路明显首选差距阈值</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>13路明显首选差距阈值</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>19路明显首选差距阈值</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>9路强制完整预算手数</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>13路强制完整预算手数</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>19路强制完整预算手数</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>探测最小候选数量</t>
         </is>
@@ -722,205 +727,210 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
+          <t>humanPolicyWeight</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>includePolicy</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>maxVisits</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>candidateLimit</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>mistakeRate</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>temperature</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>maxScoreLoss</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>visitPower</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>allowPassBeforeEndgame</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>thinkDelayMs</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>realtimeMaxVisits9</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>realtimeMaxVisits13</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>realtimeMaxVisits19</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>candidateLimit9</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>candidateLimit13</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>candidateLimit19</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="W2" s="2" t="inlineStr">
         <is>
           <t>maxScoreLoss9</t>
         </is>
       </c>
-      <c r="W2" s="2" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>maxScoreLoss13</t>
         </is>
       </c>
-      <c r="X2" s="2" t="inlineStr">
+      <c r="Y2" s="2" t="inlineStr">
         <is>
           <t>maxScoreLoss19</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>dynamicBudgetEnabled</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>probeMaxVisits9</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>probeMaxVisits13</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>probeMaxVisits19</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>openingProbeMoveLimit9</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>openingProbeMoveLimit13</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>openingProbeMoveLimit19</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>closeScoreLeadThreshold9</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>closeScoreLeadThreshold13</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>closeScoreLeadThreshold19</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>closeWinrateThreshold9</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>closeWinrateThreshold13</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>closeWinrateThreshold19</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>simpleCandidateGapThreshold9</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>simpleCandidateGapThreshold13</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>simpleCandidateGapThreshold19</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>confidentBestMoveGapThreshold9</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>confidentBestMoveGapThreshold13</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>confidentBestMoveGapThreshold19</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>forceFullBudgetMoveLimit9</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AT2" t="inlineStr">
         <is>
           <t>forceFullBudgetMoveLimit13</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
         <is>
           <t>forceFullBudgetMoveLimit19</t>
         </is>
       </c>
-      <c r="AU2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>probeMinMoveInfoCount</t>
         </is>
@@ -959,205 +969,210 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="Q3" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="R3" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="S3" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="T3" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="U3" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="W3" s="2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="W3" s="2" t="inlineStr">
+      <c r="X3" s="2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="X3" s="2" t="inlineStr">
+      <c r="Y3" s="2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AK3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AT3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AU3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="AU3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
@@ -1284,7 +1299,7 @@
           <t>#require</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y4" s="2" t="inlineStr">
         <is>
           <t>#require</t>
         </is>
@@ -1395,6 +1410,11 @@
         </is>
       </c>
       <c r="AU4" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
         <is>
           <t>#require</t>
         </is>
@@ -1403,12 +1423,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>k20_k15</t>
+          <t>k20_k18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20K-15K</t>
+          <t>20K-18K</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1418,52 +1438,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>15k</t>
+          <t>18k</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>rank_17k</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
+          <t>rank_19k</t>
+        </is>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="b">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K5" t="n">
         <v>0.85</v>
       </c>
-      <c r="K5" t="n">
-        <v>1.6</v>
-      </c>
       <c r="L5" t="n">
-        <v>30</v>
+        <v>1.8</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>450</v>
+        <v>35</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="O5" t="b">
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>420</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -1472,29 +1486,27 @@
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="U5" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="V5" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="W5" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="X5" t="n">
-        <v>30</v>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="Z5" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>35</v>
+      </c>
+      <c r="Z5" t="b">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
@@ -1558,73 +1570,70 @@
         <v>0</v>
       </c>
       <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>k14_k10</t>
+          <t>k17_k15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14K-10K</t>
+          <t>17K-15K</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14k</t>
+          <t>17k</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>15k</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>rank_12k</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
+          <t>rank_16k</t>
+        </is>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0.75</v>
+        <v>22</v>
       </c>
       <c r="K6" t="n">
-        <v>1.35</v>
+        <v>0.8</v>
       </c>
       <c r="L6" t="n">
-        <v>24</v>
+        <v>1.6</v>
       </c>
       <c r="M6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>500</v>
+        <v>30</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>460</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -1633,29 +1642,27 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="U6" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="V6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="W6" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="X6" t="n">
-        <v>24</v>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="Z6" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z6" t="b">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
@@ -1719,104 +1726,99 @@
         <v>0</v>
       </c>
       <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>k9_k7</t>
+          <t>k14_k12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9K-7K</t>
+          <t>14K-12K</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>9k</t>
+          <t>14k</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7k</t>
+          <t>12k</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>rank_8k</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>4</v>
+          <t>rank_13k</t>
+        </is>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.65</v>
+        <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>1.15</v>
+        <v>0.72</v>
       </c>
       <c r="L7" t="n">
-        <v>18</v>
+        <v>1.4</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>550</v>
+        <v>25</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="O7" t="b">
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>4</v>
+        <v>500</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="U7" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="V7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="W7" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="X7" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="Z7" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z7" t="b">
         <v>0</v>
       </c>
       <c r="AA7" t="n">
@@ -1880,104 +1882,99 @@
         <v>0</v>
       </c>
       <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>k6_k4</t>
+          <t>k11_k9</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6K-4K</t>
+          <t>11K-9K</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>6k</t>
+          <t>11k</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4k</t>
+          <t>9k</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>rank_5k</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>8</v>
+          <t>rank_10k</t>
+        </is>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>0.55</v>
+        <v>18</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0.62</v>
       </c>
       <c r="L8" t="n">
-        <v>12</v>
+        <v>1.2</v>
       </c>
       <c r="M8" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>600</v>
+        <v>18</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="O8" t="b">
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>8</v>
+        <v>540</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="U8" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="V8" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="W8" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="X8" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="Z8" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z8" t="b">
         <v>0</v>
       </c>
       <c r="AA8" t="n">
@@ -2041,104 +2038,99 @@
         <v>0</v>
       </c>
       <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>k3_k1</t>
+          <t>k8_k6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3K-1K</t>
+          <t>8K-6K</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3k</t>
+          <t>8k</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1k</t>
+          <t>6k</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>rank_2k</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>64</v>
+          <t>rank_7k</t>
+        </is>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4</v>
+        <v>16</v>
       </c>
       <c r="K9" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="L9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="O9" t="n">
-        <v>700</v>
+        <v>12</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>64</v>
+        <v>580</v>
       </c>
       <c r="Q9" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="U9" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="V9" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="W9" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="X9" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="Z9" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z9" t="b">
         <v>0</v>
       </c>
       <c r="AA9" t="n">
@@ -2202,104 +2194,99 @@
         <v>0</v>
       </c>
       <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>d1_d3</t>
+          <t>k5_k3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>业余初段-3段</t>
+          <t>5K-3K</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>5k</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3d</t>
+          <t>3k</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>rank_2d</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>160</v>
+          <t>rank_4k</t>
+        </is>
+      </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J10" t="n">
-        <v>0.22</v>
+        <v>14</v>
       </c>
       <c r="K10" t="n">
-        <v>0.62</v>
+        <v>0.38</v>
       </c>
       <c r="L10" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="O10" t="n">
-        <v>850</v>
+        <v>7.5</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>160</v>
+        <v>640</v>
       </c>
       <c r="Q10" t="n">
-        <v>128</v>
+        <v>12</v>
       </c>
       <c r="R10" t="n">
-        <v>96</v>
+        <v>8</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T10" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="U10" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="V10" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="W10" t="n">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="X10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="Z10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z10" t="b">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
@@ -2363,293 +2350,283 @@
         <v>0</v>
       </c>
       <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>d4_d5</t>
+          <t>k2_k1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>业余4段-5段</t>
+          <t>2K-1K</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4d</t>
+          <t>2k</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5d</t>
+          <t>1k</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>rank_4d</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>320</v>
+          <t>rank_1k</t>
+        </is>
+      </c>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="J11" t="n">
-        <v>0.11</v>
+        <v>10</v>
       </c>
       <c r="K11" t="n">
-        <v>0.42</v>
+        <v>0.25</v>
       </c>
       <c r="L11" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="O11" t="n">
-        <v>1050</v>
+        <v>4</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>320</v>
+        <v>720</v>
       </c>
       <c r="Q11" t="n">
-        <v>224</v>
+        <v>48</v>
       </c>
       <c r="R11" t="n">
-        <v>160</v>
+        <v>32</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="X11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="Z11" t="n">
-        <v>96</v>
+        <v>4</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z11" t="b">
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>d6</t>
+          <t>d1_d2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>业余6段</t>
+          <t>业余1段-2段</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6d</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6d</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>rank_6d</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>512</v>
+          <t>rank_1d</t>
+        </is>
+      </c>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="J12" t="n">
-        <v>0.06</v>
+        <v>8</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3</v>
+        <v>0.16</v>
       </c>
       <c r="L12" t="n">
-        <v>0.9</v>
+        <v>0.45</v>
       </c>
       <c r="M12" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="O12" t="n">
-        <v>1200</v>
+        <v>2.4</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="O12" t="b">
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>512</v>
+        <v>820</v>
       </c>
       <c r="Q12" t="n">
-        <v>320</v>
+        <v>96</v>
       </c>
       <c r="R12" t="n">
-        <v>224</v>
+        <v>64</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="T12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6</v>
+        <v>8</v>
       </c>
       <c r="W12" t="n">
-        <v>0.75</v>
+        <v>2.4</v>
       </c>
       <c r="X12" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="Z12" t="n">
-        <v>96</v>
+        <v>2.4</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z12" t="b">
+        <v>1</v>
       </c>
       <c r="AA12" t="n">
         <v>64</v>
       </c>
       <c r="AB12" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AC12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD12" t="n">
         <v>8</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AE12" t="n">
         <v>14</v>
       </c>
-      <c r="AE12" t="n">
-        <v>22</v>
-      </c>
       <c r="AF12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG12" t="n">
         <v>3</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AH12" t="n">
         <v>5</v>
       </c>
-      <c r="AH12" t="n">
-        <v>6.5</v>
-      </c>
       <c r="AI12" t="n">
-        <v>0.08</v>
+        <v>6</v>
       </c>
       <c r="AJ12" t="n">
         <v>0.08</v>
@@ -2658,481 +2635,466 @@
         <v>0.08</v>
       </c>
       <c r="AL12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AM12" t="n">
         <v>0.6</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AN12" t="n">
         <v>0.8</v>
       </c>
-      <c r="AN12" t="n">
-        <v>1</v>
-      </c>
       <c r="AO12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP12" t="n">
         <v>2</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AQ12" t="n">
         <v>2.5</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AR12" t="n">
         <v>3</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="AS12" t="n">
         <v>50</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="AT12" t="n">
         <v>90</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="AU12" t="n">
         <v>150</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="AV12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pro_1p_2p</t>
+          <t>d3_d4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>职业1段-2段</t>
+          <t>业余3段-4段</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1p</t>
+          <t>3d</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2p</t>
+          <t>4d</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>proyear_2023</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>1000</v>
+          <t>rank_3d</t>
+        </is>
+      </c>
+      <c r="F13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
       </c>
       <c r="I13" t="n">
+        <v>160</v>
+      </c>
+      <c r="J13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O13" t="b">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>940</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>160</v>
+      </c>
+      <c r="R13" t="n">
+        <v>96</v>
+      </c>
+      <c r="S13" t="n">
+        <v>64</v>
+      </c>
+      <c r="T13" t="n">
+        <v>6</v>
+      </c>
+      <c r="U13" t="n">
+        <v>6</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG13" t="n">
         <v>3</v>
       </c>
-      <c r="J13" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="AH13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AM13" t="n">
         <v>0.6</v>
       </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="O13" t="n">
-        <v>1300</v>
-      </c>
-      <c r="P13" t="n">
-        <v>640</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>384</v>
-      </c>
-      <c r="R13" t="n">
-        <v>256</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="AN13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AR13" t="n">
         <v>3</v>
       </c>
-      <c r="T13" t="n">
-        <v>3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="Z13" t="n">
-        <v>128</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>48</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR13" t="n">
+      <c r="AS13" t="n">
         <v>50</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="AT13" t="n">
         <v>90</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="AU13" t="n">
         <v>150</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="AV13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pro_3p_4p</t>
+          <t>d5_d6</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>职业3段-4段</t>
+          <t>业余5段-6段</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3p</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4p</t>
+          <t>6d</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>proyear_2023</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>1500</v>
+          <t>rank_5d</t>
+        </is>
+      </c>
+      <c r="F14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
       </c>
       <c r="I14" t="n">
+        <v>256</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="O14" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1060</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>256</v>
+      </c>
+      <c r="R14" t="n">
+        <v>160</v>
+      </c>
+      <c r="S14" t="n">
+        <v>96</v>
+      </c>
+      <c r="T14" t="n">
+        <v>5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>5</v>
+      </c>
+      <c r="V14" t="n">
+        <v>5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Z14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG14" t="n">
         <v>3</v>
       </c>
-      <c r="J14" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="O14" t="n">
-        <v>1400</v>
-      </c>
-      <c r="P14" t="n">
-        <v>720</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>448</v>
-      </c>
-      <c r="R14" t="n">
-        <v>288</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="AH14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AR14" t="n">
         <v>3</v>
       </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="Z14" t="n">
-        <v>128</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>48</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR14" t="n">
+      <c r="AS14" t="n">
         <v>50</v>
       </c>
-      <c r="AS14" t="n">
+      <c r="AT14" t="n">
         <v>90</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="AU14" t="n">
         <v>150</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="AV14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pro_5p_6p</t>
+          <t>d7_d9</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>职业5段-6段</t>
+          <t>业余7段-9段</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5p</t>
+          <t>7d</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6p</t>
+          <t>9d</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>proyear_2023</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>2200</v>
+          <t>rank_8d</t>
+        </is>
+      </c>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H15" t="b">
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>512</v>
       </c>
       <c r="J15" t="n">
-        <v>0.01</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>0.14</v>
+        <v>0.025</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3</v>
+        <v>0.16</v>
       </c>
       <c r="M15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="O15" t="n">
-        <v>1500</v>
+        <v>0.45</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O15" t="b">
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>800</v>
+        <v>1180</v>
       </c>
       <c r="Q15" t="n">
-        <v>512</v>
+        <v>384</v>
       </c>
       <c r="R15" t="n">
-        <v>320</v>
+        <v>224</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V15" t="n">
-        <v>0.18</v>
+        <v>4</v>
       </c>
       <c r="W15" t="n">
-        <v>0.25</v>
+        <v>0.45</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="Z15" t="n">
-        <v>96</v>
+        <v>0.45</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Z15" t="b">
+        <v>1</v>
       </c>
       <c r="AA15" t="n">
         <v>64</v>
       </c>
       <c r="AB15" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AC15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD15" t="n">
         <v>8</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AE15" t="n">
         <v>14</v>
       </c>
-      <c r="AE15" t="n">
-        <v>24</v>
-      </c>
       <c r="AF15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG15" t="n">
         <v>3</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AH15" t="n">
         <v>5</v>
       </c>
-      <c r="AH15" t="n">
-        <v>7</v>
-      </c>
       <c r="AI15" t="n">
-        <v>0.08</v>
+        <v>6</v>
       </c>
       <c r="AJ15" t="n">
         <v>0.08</v>
@@ -3141,55 +3103,58 @@
         <v>0.08</v>
       </c>
       <c r="AL15" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AM15" t="n">
         <v>0.6</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AN15" t="n">
         <v>0.8</v>
       </c>
-      <c r="AN15" t="n">
-        <v>1</v>
-      </c>
       <c r="AO15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP15" t="n">
         <v>2</v>
       </c>
-      <c r="AP15" t="n">
+      <c r="AQ15" t="n">
         <v>2.5</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AR15" t="n">
         <v>3</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="AS15" t="n">
         <v>50</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="AT15" t="n">
         <v>90</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="AU15" t="n">
         <v>150</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="AV15" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pro_7p_8p</t>
+          <t>modern_pro</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>职业7段-8段</t>
+          <t>现代职业</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>7p</t>
+          <t>1p</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8p</t>
+          <t>9p</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3197,44 +3162,38 @@
           <t>proyear_2023</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>3000</v>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>800</v>
       </c>
       <c r="J16" t="n">
-        <v>0.005</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L16" t="n">
         <v>0.1</v>
       </c>
-      <c r="L16" t="n">
-        <v>0.2</v>
-      </c>
       <c r="M16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="O16" t="n">
-        <v>1550</v>
+        <v>0.25</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O16" t="b">
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>800</v>
+        <v>1280</v>
       </c>
       <c r="Q16" t="n">
         <v>512</v>
@@ -3243,57 +3202,55 @@
         <v>320</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>192</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V16" t="n">
-        <v>0.12</v>
+        <v>3</v>
       </c>
       <c r="W16" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="X16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="Z16" t="n">
-        <v>96</v>
+        <v>0.25</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Z16" t="b">
+        <v>1</v>
       </c>
       <c r="AA16" t="n">
         <v>64</v>
       </c>
       <c r="AB16" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AC16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD16" t="n">
         <v>8</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AE16" t="n">
         <v>14</v>
       </c>
-      <c r="AE16" t="n">
-        <v>24</v>
-      </c>
       <c r="AF16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG16" t="n">
         <v>3</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AH16" t="n">
         <v>5</v>
       </c>
-      <c r="AH16" t="n">
-        <v>7</v>
-      </c>
       <c r="AI16" t="n">
-        <v>0.08</v>
+        <v>6</v>
       </c>
       <c r="AJ16" t="n">
         <v>0.08</v>
@@ -3302,194 +3259,36 @@
         <v>0.08</v>
       </c>
       <c r="AL16" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AM16" t="n">
         <v>0.6</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="AN16" t="n">
         <v>0.8</v>
       </c>
-      <c r="AN16" t="n">
-        <v>1</v>
-      </c>
       <c r="AO16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP16" t="n">
         <v>2</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AQ16" t="n">
         <v>2.5</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AR16" t="n">
         <v>3</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="AS16" t="n">
         <v>50</v>
       </c>
-      <c r="AS16" t="n">
+      <c r="AT16" t="n">
         <v>90</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="AU16" t="n">
         <v>150</v>
       </c>
-      <c r="AU16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>pro_9p</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>职业9段</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>9p</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>9p</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>proyear_2023</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>4000</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="O17" t="n">
-        <v>1600</v>
-      </c>
-      <c r="P17" t="n">
-        <v>800</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>512</v>
-      </c>
-      <c r="R17" t="n">
-        <v>320</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="Z17" t="n">
-        <v>96</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>64</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>32</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>50</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>90</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>150</v>
-      </c>
-      <c r="AU17" t="n">
+      <c r="AV16" t="n">
         <v>1</v>
       </c>
     </row>
